--- a/VMISP/Upload/Files/ExcelImport/IAC.xlsx
+++ b/VMISP/Upload/Files/ExcelImport/IAC.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0340920\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\offic\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD415A9B-F966-454A-8A1A-3393847803F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IAC" sheetId="2" r:id="rId1"/>
+    <sheet name="IAC" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>ROWNO</t>
   </si>
@@ -105,70 +106,25 @@
     <t>NEWCIRCLESOLID</t>
   </si>
   <si>
-    <t>M01</t>
-  </si>
-  <si>
-    <t>M02</t>
-  </si>
-  <si>
-    <t>V01</t>
-  </si>
-  <si>
-    <t>V02</t>
-  </si>
-  <si>
-    <t>GAURAV</t>
-  </si>
-  <si>
-    <t>VISHRAM</t>
-  </si>
-  <si>
-    <t>DELHI</t>
-  </si>
-  <si>
-    <t>HOITD</t>
-  </si>
-  <si>
-    <t>SANSAD MARG</t>
-  </si>
-  <si>
-    <t>NORTH DELHI</t>
-  </si>
-  <si>
-    <t>VISH RAM MEENA</t>
-  </si>
-  <si>
-    <t>GAURAV KUMAR</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>HRD</t>
-  </si>
-  <si>
-    <t>UAT</t>
-  </si>
-  <si>
     <t>BANKNAME</t>
   </si>
   <si>
-    <t>PNB</t>
-  </si>
-  <si>
-    <t>eOBC</t>
-  </si>
-  <si>
-    <t>IAC11</t>
-  </si>
-  <si>
-    <t>IAC22</t>
+    <t>DESIGNATION</t>
+  </si>
+  <si>
+    <t>SCALE</t>
+  </si>
+  <si>
+    <t>TMSACREFNO</t>
+  </si>
+  <si>
+    <t>jks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -195,11 +151,10 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyProtection="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,40 +173,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:AC3" totalsRowShown="0">
-  <autoFilter ref="A1:AC3"/>
-  <tableColumns count="29">
-    <tableColumn id="1" name="ROWNO"/>
-    <tableColumn id="2" name="IACNO"/>
-    <tableColumn id="3" name="MEETNO"/>
-    <tableColumn id="4" name="IACNO_1"/>
-    <tableColumn id="5" name="VIGNO"/>
-    <tableColumn id="6" name="ACCUSED"/>
-    <tableColumn id="7" name="PFNUMBER"/>
-    <tableColumn id="8" name="DTRET"/>
-    <tableColumn id="9" name="SOURCE"/>
-    <tableColumn id="10" name="PRESENTPOSTING"/>
-    <tableColumn id="11" name="NAMEOFTHEBRANCH"/>
-    <tableColumn id="12" name="ZONE"/>
-    <tableColumn id="13" name="CIRCLEOFFICE"/>
-    <tableColumn id="14" name="DTIAC"/>
-    <tableColumn id="15" name="ACNAME"/>
-    <tableColumn id="16" name="RECDT"/>
-    <tableColumn id="17" name="DATEIADNOTE"/>
-    <tableColumn id="18" name="NATURECASE"/>
-    <tableColumn id="19" name="AMOUNT"/>
-    <tableColumn id="20" name="DA"/>
-    <tableColumn id="21" name="STATUS"/>
-    <tableColumn id="22" name="DAVIEW"/>
-    <tableColumn id="23" name="IACVIEW"/>
-    <tableColumn id="24" name="CVOVIEW"/>
-    <tableColumn id="25" name="CLOSUREDT"/>
-    <tableColumn id="26" name="STATUSCODE"/>
-    <tableColumn id="27" name="NEWZONESOLID"/>
-    <tableColumn id="28" name="NEWCIRCLESOLID"/>
-    <tableColumn id="29" name="BANKNAME"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AF2" totalsRowShown="0">
+  <autoFilter ref="A1:AF2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="32">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ROWNO"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="IACNO"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="MEETNO"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="IACNO_1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="VIGNO"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ACCUSED"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="PFNUMBER"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="DTRET"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="SOURCE"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="PRESENTPOSTING"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="NAMEOFTHEBRANCH"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="ZONE"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="CIRCLEOFFICE"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="DTIAC"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="ACNAME"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="RECDT"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="DATEIADNOTE"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="NATURECASE"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="AMOUNT"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="DA"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="STATUS"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="DAVIEW"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="IACVIEW"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="CVOVIEW"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="CLOSUREDT"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="STATUSCODE"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="NEWZONESOLID"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="NEWCIRCLESOLID"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="BANKNAME"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="DESIGNATION"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="SCALE"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="TMSACREFNO"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -539,41 +497,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="15.42578125" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" customWidth="1"/>
-    <col min="21" max="21" width="9.28515625" customWidth="1"/>
-    <col min="22" max="22" width="10.140625" customWidth="1"/>
-    <col min="23" max="23" width="10.7109375" customWidth="1"/>
-    <col min="24" max="24" width="11.5703125" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" customWidth="1"/>
-    <col min="26" max="26" width="14.140625" customWidth="1"/>
-    <col min="27" max="27" width="17.28515625" customWidth="1"/>
-    <col min="28" max="28" width="18.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,179 +587,33 @@
         <v>27</v>
       </c>
       <c r="AC1" t="s">
-        <v>43</v>
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
+        <v>987</v>
+      </c>
+      <c r="B2">
+        <v>654</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2">
-        <v>340987</v>
-      </c>
-      <c r="H2" s="1">
-        <v>44067</v>
-      </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="1">
-        <v>44061</v>
-      </c>
-      <c r="O2" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="1">
-        <v>44037</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>44066</v>
-      </c>
-      <c r="R2" t="s">
-        <v>40</v>
-      </c>
-      <c r="S2">
-        <v>500</v>
-      </c>
-      <c r="T2" t="s">
-        <v>41</v>
-      </c>
-      <c r="U2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" t="s">
-        <v>40</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>543500</v>
+        <v>100002</v>
       </c>
       <c r="AB2">
-        <v>378000</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3">
-        <v>340920</v>
-      </c>
-      <c r="H3" s="1">
-        <v>44067</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N3" s="1">
-        <v>44061</v>
-      </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="1">
-        <v>44037</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>44066</v>
-      </c>
-      <c r="R3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S3">
-        <v>600</v>
-      </c>
-      <c r="T3" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" t="s">
-        <v>40</v>
-      </c>
-      <c r="W3" t="s">
-        <v>40</v>
-      </c>
-      <c r="X3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Z3">
-        <v>1</v>
-      </c>
-      <c r="AA3">
-        <v>543500</v>
-      </c>
-      <c r="AB3">
-        <v>383400</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>45</v>
+        <v>200004</v>
       </c>
     </row>
   </sheetData>
